--- a/data/proteomics/organell_protein_ratio_jianye.xlsx
+++ b/data/proteomics/organell_protein_ratio_jianye.xlsx
@@ -1145,7 +1145,7 @@
         <v>0.4701297768070277</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009066308121122883</v>
+        <v>0.0009066308121122885</v>
       </c>
       <c r="D2" t="n">
         <v>0.000996805047153701</v>
@@ -1154,13 +1154,13 @@
         <v>0.03163585548081622</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2668677881882346</v>
+        <v>0.2668677881882349</v>
       </c>
       <c r="G2" t="n">
         <v>0.5748854790508313</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2883727858728327</v>
+        <v>0.288372785872833</v>
       </c>
       <c r="I2" t="n">
         <v>0.05280371670840953</v>
@@ -1172,16 +1172,16 @@
         <v>0.07111491926977408</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02687342888336699</v>
+        <v>0.026873428883367</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008375639051878312</v>
+        <v>0.0008375639051878315</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02474487533664501</v>
+        <v>0.024744875336645</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01147730980778303</v>
+        <v>0.01147730980778302</v>
       </c>
       <c r="P2" t="n">
         <v>0.004355727406914132</v>
@@ -1205,16 +1205,16 @@
         <v>0.001825634027371698</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0412694221134305</v>
+        <v>0.04126942211343047</v>
       </c>
       <c r="X2" t="n">
-        <v>6.120176094150368e-05</v>
+        <v>6.120176094150365e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00499021835183019</v>
+        <v>0.004990218351830194</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001687768870440512</v>
+        <v>0.001687768870440511</v>
       </c>
       <c r="AA2" t="n">
         <v>0.01864931080156966</v>
@@ -1233,7 +1233,7 @@
         <v>0.06978286840554844</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.02554361133369724</v>
+        <v>0.02554361133369725</v>
       </c>
       <c r="AH2" t="n">
         <v>0.002602995471137663</v>
@@ -1248,7 +1248,7 @@
         <v>0.02099836654689091</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.001149775670666102</v>
+        <v>0.001149775670666101</v>
       </c>
       <c r="AM2" t="n">
         <v>0.0005101218242704829</v>
@@ -1266,7 +1266,7 @@
         <v>0.002907365142082945</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.00305322948598601</v>
+        <v>0.003053229485986011</v>
       </c>
       <c r="AS2" t="n">
         <v>0.0001065035366824046</v>
@@ -1287,7 +1287,7 @@
         <v>0.001048741237429211</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.02903375798224525</v>
+        <v>0.02903375798224526</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.001087724965459433</v>
@@ -1296,7 +1296,7 @@
         <v>0.0001268147602891467</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.04237781230942052</v>
+        <v>0.04237781230942056</v>
       </c>
       <c r="BC2" t="n">
         <v>0.01457893960669168</v>
@@ -1326,7 +1326,7 @@
         <v>0.01684454325804541</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.0002117873670510653</v>
+        <v>0.0002117873670510654</v>
       </c>
       <c r="BM2" t="n">
         <v>0.06441963191107093</v>
@@ -1435,7 +1435,7 @@
         <v>0.0004751137984999275</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.0003035772239851064</v>
+        <v>0.0003035772239851065</v>
       </c>
       <c r="CX2" t="n">
         <v>0.006519477864802944</v>
@@ -1456,7 +1456,7 @@
         <v>0.0008369617982276101</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.002691413153989937</v>
+        <v>0.002691413153989938</v>
       </c>
       <c r="DE2" t="n">
         <v>7.095401579876364e-05</v>
@@ -1468,13 +1468,13 @@
         <v>0.009286563060831303</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.002050158678091753</v>
+        <v>0.002050158678091752</v>
       </c>
       <c r="DI2" t="n">
         <v>0.0003198775683593435</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.0002160596495082294</v>
+        <v>0.0002160596495082293</v>
       </c>
       <c r="DK2" t="n">
         <v>0.002172149418232885</v>
@@ -1501,13 +1501,13 @@
         <v>1.320304209615597e-05</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.003046078282300688</v>
+        <v>0.003046078282300687</v>
       </c>
       <c r="DT2" t="n">
         <v>0.0008552857843604045</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.0008048622899086593</v>
+        <v>0.0008048622899086596</v>
       </c>
       <c r="DV2" t="n">
         <v>0.0004581363297348337</v>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="ED2" t="inlineStr"/>
       <c r="EE2" t="n">
-        <v>0.000233310643931657</v>
+        <v>0.0002333106439316571</v>
       </c>
       <c r="EF2" t="n">
         <v>3.32400614698221e-06</v>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4697312362062084</v>
+        <v>0.4697312362062082</v>
       </c>
       <c r="C3" t="n">
         <v>0.0008869533152768077</v>
@@ -1580,10 +1580,10 @@
         <v>0.03014410804827897</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2542450068872546</v>
+        <v>0.254245006887254</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5624305440295322</v>
+        <v>0.5624305440295327</v>
       </c>
       <c r="H3" t="n">
         <v>0.2894209109898178</v>
@@ -1598,7 +1598,7 @@
         <v>0.06850637337552939</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02813999011241572</v>
+        <v>0.02813999011241568</v>
       </c>
       <c r="M3" t="n">
         <v>0.000977809608398013</v>
@@ -1649,7 +1649,7 @@
         <v>0.0005950107981188924</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.01883054026648262</v>
+        <v>0.01883054026648263</v>
       </c>
       <c r="AD3" t="n">
         <v>3.725403501811415e-05</v>
@@ -1668,7 +1668,7 @@
         <v>0.0009658814057756704</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.001534509336062126</v>
+        <v>0.001534509336062125</v>
       </c>
       <c r="AK3" t="n">
         <v>0.02185361400818031</v>
@@ -1677,7 +1677,7 @@
         <v>0.001097635431238419</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0005111125501660145</v>
+        <v>0.0005111125501660147</v>
       </c>
       <c r="AN3" t="n">
         <v>0.0005108326361980628</v>
@@ -1692,7 +1692,7 @@
         <v>0.002990343711342321</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.003053830579309739</v>
+        <v>0.00305383057930974</v>
       </c>
       <c r="AS3" t="n">
         <v>0.0001060201447939805</v>
@@ -1716,7 +1716,7 @@
         <v>0.03023747389567964</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.001302327592675242</v>
+        <v>0.001302327592675243</v>
       </c>
       <c r="BA3" t="n">
         <v>0.000121811648722084</v>
@@ -1734,7 +1734,7 @@
         <v>0.001843127567282762</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.0006642469909737132</v>
+        <v>0.0006642469909737135</v>
       </c>
       <c r="BG3" t="n">
         <v>0.001403304653657928</v>
@@ -1767,7 +1767,7 @@
         <v>0.0006725732813788176</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0007915975985208017</v>
+        <v>0.0007915975985208015</v>
       </c>
       <c r="BR3" t="n">
         <v>0.00017892727271738</v>
@@ -1788,7 +1788,7 @@
         <v>9.043358122945766e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.001894705295368144</v>
+        <v>0.001894705295368143</v>
       </c>
       <c r="BY3" t="n">
         <v>0.000104772722546597</v>
@@ -1803,7 +1803,7 @@
         <v>0.0004095784467551776</v>
       </c>
       <c r="CC3" t="n">
-        <v>7.227467146825973e-05</v>
+        <v>7.227467146825969e-05</v>
       </c>
       <c r="CD3" t="n">
         <v>0.0003469037293173168</v>
@@ -1834,7 +1834,7 @@
         <v>6.136081024838216e-06</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.0001992492022964491</v>
+        <v>0.000199249202296449</v>
       </c>
       <c r="CO3" t="n">
         <v>0.004172847639593183</v>
@@ -1849,7 +1849,7 @@
         <v>0.001708131176756477</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.0001826332171272021</v>
+        <v>0.0001826332171272022</v>
       </c>
       <c r="CT3" t="n">
         <v>0.0005580395267312362</v>
@@ -1858,7 +1858,7 @@
         <v>0.0004559871376892735</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.0004898833517079646</v>
+        <v>0.0004898833517079643</v>
       </c>
       <c r="CW3" t="n">
         <v>0.0002857996437370407</v>
@@ -1882,7 +1882,7 @@
         <v>0.0008241773102684649</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.002429185243004408</v>
+        <v>0.002429185243004409</v>
       </c>
       <c r="DE3" t="n">
         <v>7.901050210829878e-05</v>
@@ -1891,7 +1891,7 @@
         <v>0.0004437912956409151</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.008800096095799832</v>
+        <v>0.008800096095799835</v>
       </c>
       <c r="DH3" t="n">
         <v>0.001959691136784027</v>
@@ -1918,7 +1918,7 @@
         <v>0.001695741140542341</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.07178007246901852</v>
+        <v>0.07178007246901859</v>
       </c>
       <c r="DQ3" t="n">
         <v>5.023980261420424e-05</v>
@@ -1939,7 +1939,7 @@
         <v>0.0004707439025153652</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.0001888504193938645</v>
+        <v>0.0001888504193938646</v>
       </c>
       <c r="DX3" t="n">
         <v>0.0003772730614976709</v>
@@ -1951,7 +1951,7 @@
         <v>0.0008126780307712931</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.0003094439126066839</v>
+        <v>0.000309443912606684</v>
       </c>
       <c r="EB3" t="n">
         <v>0.0001910970218956728</v>
@@ -1973,7 +1973,7 @@
         <v>2.445370683019079e-05</v>
       </c>
       <c r="EI3" t="n">
-        <v>5.930699713170883e-05</v>
+        <v>5.93069971317088e-05</v>
       </c>
       <c r="EJ3" t="n">
         <v>1.580046949513696e-05</v>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4427010824280561</v>
+        <v>0.4427010824280564</v>
       </c>
       <c r="C4" t="n">
         <v>0.0008841314819842183</v>
@@ -2006,13 +2006,13 @@
         <v>0.03291568455165914</v>
       </c>
       <c r="F4" t="n">
-        <v>0.225750304918102</v>
+        <v>0.2257503049181022</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5406132376290328</v>
+        <v>0.5406132376290333</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2611804991616697</v>
+        <v>0.2611804991616698</v>
       </c>
       <c r="I4" t="n">
         <v>0.04280743831077345</v>
@@ -2024,7 +2024,7 @@
         <v>0.05054215732188105</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03140749065292335</v>
+        <v>0.03140749065292332</v>
       </c>
       <c r="M4" t="n">
         <v>0.00126403835760666</v>
@@ -2033,19 +2033,19 @@
         <v>0.02507047413789396</v>
       </c>
       <c r="O4" t="n">
-        <v>0.009961062327987618</v>
+        <v>0.009961062327987614</v>
       </c>
       <c r="P4" t="n">
         <v>0.004855046590331344</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002801861753727941</v>
+        <v>0.002801861753727942</v>
       </c>
       <c r="R4" t="n">
         <v>0.005705121414226342</v>
       </c>
       <c r="S4" t="n">
-        <v>0.006536951940469789</v>
+        <v>0.006536951940469795</v>
       </c>
       <c r="T4" t="n">
         <v>0.01381168822337765</v>
@@ -2069,7 +2069,7 @@
         <v>0.002033851574412502</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02311286167134515</v>
+        <v>0.02311286167134514</v>
       </c>
       <c r="AB4" t="n">
         <v>0.0006103929741212887</v>
@@ -2082,19 +2082,19 @@
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>0.0633126394581499</v>
+        <v>0.06331263945814992</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.02143482450430328</v>
+        <v>0.02143482450430327</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.002912261859586388</v>
+        <v>0.002912261859586391</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.0009397853117095095</v>
+        <v>0.0009397853117095091</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.001663097894681753</v>
+        <v>0.001663097894681754</v>
       </c>
       <c r="AK4" t="n">
         <v>0.02454854497439962</v>
@@ -2115,7 +2115,7 @@
         <v>0.0005686792883718357</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.003185601576480692</v>
+        <v>0.003185601576480695</v>
       </c>
       <c r="AR4" t="n">
         <v>0.003296633938797981</v>
@@ -2148,10 +2148,10 @@
         <v>0.0001142765186471539</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.0341747763038892</v>
+        <v>0.03417477630388924</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.01279775873633513</v>
+        <v>0.01279775873633512</v>
       </c>
       <c r="BD4" t="n">
         <v>0.01100344792126843</v>
@@ -2160,13 +2160,13 @@
         <v>0.001950364398558822</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.0006526972097775609</v>
+        <v>0.0006526972097775606</v>
       </c>
       <c r="BG4" t="n">
         <v>0.001416768964800287</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.01006043412068267</v>
+        <v>0.01006043412068268</v>
       </c>
       <c r="BI4" t="n">
         <v>0.0006817262734564126</v>
@@ -2190,7 +2190,7 @@
         <v>7.005523011788874e-05</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0005815154843429036</v>
+        <v>0.000581515484342904</v>
       </c>
       <c r="BQ4" t="n">
         <v>0.001033130240732559</v>
@@ -2205,7 +2205,7 @@
         <v>0.00529624178095502</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.009139129970847213</v>
+        <v>0.009139129970847207</v>
       </c>
       <c r="BV4" t="n">
         <v>0.005003775985429937</v>
@@ -2229,13 +2229,13 @@
         <v>0.0004602714480321943</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.782682560335746e-05</v>
+        <v>6.782682560335743e-05</v>
       </c>
       <c r="CD4" t="n">
         <v>0.0004268286038943762</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.004298117972618289</v>
+        <v>0.004298117972618292</v>
       </c>
       <c r="CF4" t="n">
         <v>0.001292320562644245</v>
@@ -2293,13 +2293,13 @@
         <v>0.005957432348109245</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0001174267313237842</v>
+        <v>0.0001174267313237843</v>
       </c>
       <c r="CZ4" t="n">
         <v>0.0003055670229208531</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0009931202135908075</v>
+        <v>0.0009931202135908073</v>
       </c>
       <c r="DB4" t="n">
         <v>0.0006542535786198395</v>
@@ -2308,7 +2308,7 @@
         <v>0.000799972166866795</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.002505822725862676</v>
+        <v>0.002505822725862675</v>
       </c>
       <c r="DE4" t="n">
         <v>0.0001143850434117947</v>
@@ -2329,7 +2329,7 @@
         <v>0.0002613714152980511</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.00238054701154554</v>
+        <v>0.002380547011545541</v>
       </c>
       <c r="DL4" t="n">
         <v>0.0003600720055336282</v>
@@ -2344,7 +2344,7 @@
         <v>0.002175009477040888</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.08744541242854886</v>
+        <v>0.08744541242854884</v>
       </c>
       <c r="DQ4" t="n">
         <v>4.452683554945423e-05</v>
@@ -2377,7 +2377,7 @@
         <v>0.0007322771349499179</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.0003644586959626325</v>
+        <v>0.0003644586959626328</v>
       </c>
       <c r="EB4" t="n">
         <v>0.0002210867024127552</v>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4302917210149803</v>
+        <v>0.4302917210149795</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0008907398931513033</v>
+        <v>0.0008907398931513036</v>
       </c>
       <c r="D5" t="n">
         <v>0.001028000438513568</v>
@@ -2434,10 +2434,10 @@
         <v>0.03389273170844977</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2117453172515465</v>
+        <v>0.2117453172515461</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5353894819099604</v>
+        <v>0.5353894819099612</v>
       </c>
       <c r="H5" t="n">
         <v>0.2475798672246243</v>
@@ -2461,7 +2461,7 @@
         <v>0.02365192391914337</v>
       </c>
       <c r="O5" t="n">
-        <v>0.009440356804696593</v>
+        <v>0.009440356804696591</v>
       </c>
       <c r="P5" t="n">
         <v>0.004730794590152006</v>
@@ -2470,10 +2470,10 @@
         <v>0.002306697959849281</v>
       </c>
       <c r="R5" t="n">
-        <v>0.005612449827191477</v>
+        <v>0.005612449827191472</v>
       </c>
       <c r="S5" t="n">
-        <v>0.006472566479119694</v>
+        <v>0.006472566479119692</v>
       </c>
       <c r="T5" t="n">
         <v>0.01410665601290341</v>
@@ -2494,16 +2494,16 @@
         <v>0.004891280467241178</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002017704447126591</v>
+        <v>0.002017704447126592</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02509641747711692</v>
+        <v>0.02509641747711691</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0006041376948482412</v>
+        <v>0.0006041376948482415</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0170260864497145</v>
+        <v>0.01702608644971451</v>
       </c>
       <c r="AD5" t="n">
         <v>3.884086450130029e-05</v>
@@ -2513,13 +2513,13 @@
         <v>0.06249727264102161</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.01960791207318191</v>
+        <v>0.0196079120731819</v>
       </c>
       <c r="AH5" t="n">
         <v>0.003022018765920106</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0009459167166370011</v>
+        <v>0.0009459167166370009</v>
       </c>
       <c r="AJ5" t="n">
         <v>0.001618788431496521</v>
@@ -2567,7 +2567,7 @@
         <v>0.001470380271723591</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.03914523888490774</v>
+        <v>0.03914523888490777</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.001287118531169543</v>
@@ -2633,7 +2633,7 @@
         <v>0.005890666521938925</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.008491456951512039</v>
+        <v>0.008491456951512042</v>
       </c>
       <c r="BV5" t="n">
         <v>0.005124877380372054</v>
@@ -2654,7 +2654,7 @@
         <v>1.774061129330436e-05</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.0004636170625882966</v>
+        <v>0.0004636170625882964</v>
       </c>
       <c r="CC5" t="n">
         <v>7.122152528605174e-05</v>
@@ -2695,7 +2695,7 @@
         <v>0.000449328661034962</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.00360109410878149</v>
+        <v>0.003601094108781493</v>
       </c>
       <c r="CR5" t="n">
         <v>0.002039981020352701</v>
@@ -2707,7 +2707,7 @@
         <v>0.0006732381835331732</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0006242194735676051</v>
+        <v>0.0006242194735676055</v>
       </c>
       <c r="CV5" t="n">
         <v>0.000539262165492876</v>
@@ -2743,7 +2743,7 @@
         <v>0.0004512989263425498</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.00847088636578704</v>
+        <v>0.008470886365787036</v>
       </c>
       <c r="DH5" t="n">
         <v>0.002196224277930979</v>
@@ -2755,7 +2755,7 @@
         <v>0.000258108893307667</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.002464720704087507</v>
+        <v>0.002464720704087506</v>
       </c>
       <c r="DL5" t="n">
         <v>0.0003462561634058512</v>
@@ -2767,10 +2767,10 @@
         <v>8.540239402299917e-05</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.002222578767771982</v>
+        <v>0.002222578767771981</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.09740055322390193</v>
+        <v>0.09740055322390198</v>
       </c>
       <c r="DQ5" t="n">
         <v>4.0478191533394e-05</v>
@@ -2858,13 +2858,13 @@
         <v>0.0356648644400828</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1987796473186527</v>
+        <v>0.1987796473186526</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5290305186745271</v>
+        <v>0.5290305186745279</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2299264514502334</v>
+        <v>0.2299264514502333</v>
       </c>
       <c r="I6" t="n">
         <v>0.03867548664349214</v>
@@ -2876,7 +2876,7 @@
         <v>0.03560617933748741</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02776260699003847</v>
+        <v>0.02776260699003846</v>
       </c>
       <c r="M6" t="n">
         <v>0.001438088301468049</v>
@@ -2921,7 +2921,7 @@
         <v>0.001976306422366146</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.02783189691965789</v>
+        <v>0.02783189691965788</v>
       </c>
       <c r="AB6" t="n">
         <v>0.0006251168255701511</v>
@@ -2940,16 +2940,16 @@
         <v>0.01758408744023504</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.003180333592497125</v>
+        <v>0.003180333592497124</v>
       </c>
       <c r="AI6" t="n">
         <v>0.0009302182312428231</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.001550121719593844</v>
+        <v>0.001550121719593843</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.02912279651337363</v>
+        <v>0.02912279651337364</v>
       </c>
       <c r="AL6" t="n">
         <v>0.001070417799421117</v>
@@ -2964,13 +2964,13 @@
         <v>0.001584729317797654</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.0005761026459937132</v>
+        <v>0.0005761026459937135</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.003097478875009221</v>
+        <v>0.003097478875009222</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.003224878040109921</v>
+        <v>0.00322487804010992</v>
       </c>
       <c r="AS6" t="n">
         <v>8.480710804632455e-05</v>
@@ -3021,7 +3021,7 @@
         <v>0.009006379814305354</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.000639833506901647</v>
+        <v>0.0006398335069016473</v>
       </c>
       <c r="BJ6" t="n">
         <v>1.578693199865398e-05</v>
@@ -3057,13 +3057,13 @@
         <v>0.007061565323025832</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.008362726574660938</v>
+        <v>0.008362726574660934</v>
       </c>
       <c r="BV6" t="n">
         <v>0.00513894878416937</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.777126748578314e-05</v>
+        <v>8.77712674857831e-05</v>
       </c>
       <c r="BX6" t="n">
         <v>0.001548621710372254</v>
@@ -3102,7 +3102,7 @@
         <v>0.0001614551491847752</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.001814601735142922</v>
+        <v>0.001814601735142923</v>
       </c>
       <c r="CK6" t="inlineStr"/>
       <c r="CL6" t="n">
@@ -3148,7 +3148,7 @@
         <v>0.000107719080666305</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0003610410782323371</v>
+        <v>0.000361041078232337</v>
       </c>
       <c r="DA6" t="n">
         <v>0.0009833548604587475</v>
@@ -3251,7 +3251,7 @@
         <v>2.850490453073292e-05</v>
       </c>
       <c r="EI6" t="n">
-        <v>6.046317849200862e-05</v>
+        <v>6.046317849200866e-05</v>
       </c>
       <c r="EJ6" t="n">
         <v>1.759030777184748e-05</v>
@@ -3284,13 +3284,13 @@
         <v>0.0372819148907283</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1890869734863404</v>
+        <v>0.1890869734863403</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5308206114613083</v>
+        <v>0.530820611461309</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2189298888844606</v>
+        <v>0.2189298888844607</v>
       </c>
       <c r="I7" t="n">
         <v>0.03667753376161742</v>
@@ -3302,7 +3302,7 @@
         <v>0.03115316005190067</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02441863224440297</v>
+        <v>0.02441863224440296</v>
       </c>
       <c r="M7" t="n">
         <v>0.001461695721674406</v>
@@ -3314,7 +3314,7 @@
         <v>0.008700507493081456</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00441472062560659</v>
+        <v>0.004414720625606586</v>
       </c>
       <c r="Q7" t="n">
         <v>0.001518307409269101</v>
@@ -3347,20 +3347,20 @@
         <v>0.001880482289151838</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02925917250358857</v>
+        <v>0.02925917250358859</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0006258739080571083</v>
+        <v>0.000625873908057108</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.01540524184328389</v>
+        <v>0.01540524184328388</v>
       </c>
       <c r="AD7" t="n">
         <v>4.28736254847017e-05</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>0.06495151929551204</v>
+        <v>0.06495151929551202</v>
       </c>
       <c r="AG7" t="n">
         <v>0.01685215058890327</v>
@@ -3369,13 +3369,13 @@
         <v>0.003170120203742954</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0008788887049419299</v>
+        <v>0.0008788887049419296</v>
       </c>
       <c r="AJ7" t="n">
         <v>0.001477570098736048</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.03114479339525339</v>
+        <v>0.03114479339525338</v>
       </c>
       <c r="AL7" t="n">
         <v>0.001034046042618761</v>
@@ -3393,7 +3393,7 @@
         <v>0.0005472415333049555</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.003175783436979974</v>
+        <v>0.003175783436979973</v>
       </c>
       <c r="AR7" t="n">
         <v>0.003052866001679624</v>
@@ -3408,7 +3408,7 @@
         <v>0.000417795542482106</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.001420741782703834</v>
+        <v>0.001420741782703835</v>
       </c>
       <c r="AW7" t="n">
         <v>0.003874634954061206</v>
@@ -3417,7 +3417,7 @@
         <v>0.00156186269565875</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.04606645438517814</v>
+        <v>0.0460664543851781</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.001509105024100107</v>
@@ -3444,7 +3444,7 @@
         <v>0.001429548475416827</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.008360738787730677</v>
+        <v>0.008360738787730674</v>
       </c>
       <c r="BI7" t="n">
         <v>0.000614573557062306</v>
@@ -3453,13 +3453,13 @@
         <v>1.040153024219886e-05</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.006076686458026284</v>
+        <v>0.006076686458026281</v>
       </c>
       <c r="BL7" t="n">
         <v>0.000258453334719393</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.07396517651560797</v>
+        <v>0.07396517651560794</v>
       </c>
       <c r="BN7" t="n">
         <v>0.001413513942890958</v>
@@ -3593,7 +3593,7 @@
         <v>0.0004240089365035634</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.007578395095907926</v>
+        <v>0.007578395095907929</v>
       </c>
       <c r="DH7" t="n">
         <v>0.00222538230496221</v>
@@ -3708,13 +3708,13 @@
         <v>0.03735636153566424</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1882128783430856</v>
+        <v>0.1882128783430859</v>
       </c>
       <c r="G8" t="n">
         <v>0.5351073547522501</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2247253380687526</v>
+        <v>0.2247253380687525</v>
       </c>
       <c r="I8" t="n">
         <v>0.03722777799733244</v>
@@ -3732,7 +3732,7 @@
         <v>0.001304909378755315</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01829276363357241</v>
+        <v>0.0182927636335724</v>
       </c>
       <c r="O8" t="n">
         <v>0.008485671647548022</v>
@@ -3750,7 +3750,7 @@
         <v>0.006222712054299446</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01414704862133063</v>
+        <v>0.01414704862133062</v>
       </c>
       <c r="U8" t="n">
         <v>0.0004119358475996371</v>
@@ -3759,22 +3759,22 @@
         <v>0.00174254112677569</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02276163018435192</v>
+        <v>0.02276163018435191</v>
       </c>
       <c r="X8" t="n">
-        <v>6.222265297685686e-05</v>
+        <v>6.222265297685683e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.00470165937142367</v>
+        <v>0.004701659371423667</v>
       </c>
       <c r="Z8" t="n">
         <v>0.001886416442025391</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03029590507927846</v>
+        <v>0.03029590507927845</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0006069266884917987</v>
+        <v>0.0006069266884917983</v>
       </c>
       <c r="AC8" t="n">
         <v>0.0141068652519799</v>
@@ -3787,13 +3787,13 @@
         <v>0.06900615958074455</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.01774080390597978</v>
+        <v>0.01774080390597979</v>
       </c>
       <c r="AH8" t="n">
         <v>0.003124033892803256</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0008579012903568025</v>
+        <v>0.0008579012903568029</v>
       </c>
       <c r="AJ8" t="n">
         <v>0.001488233523834212</v>
@@ -3817,7 +3817,7 @@
         <v>0.0005160997479305583</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.003099423473450346</v>
+        <v>0.003099423473450347</v>
       </c>
       <c r="AR8" t="n">
         <v>0.003027496977310177</v>
@@ -3841,7 +3841,7 @@
         <v>0.001493299054135424</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.04790570562735744</v>
+        <v>0.0479057056273574</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.001253773305525848</v>
@@ -3850,7 +3850,7 @@
         <v>0.0001124370067924376</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.02156503475702056</v>
+        <v>0.02156503475702055</v>
       </c>
       <c r="BC8" t="n">
         <v>0.01080603792292194</v>
@@ -3859,7 +3859,7 @@
         <v>0.01565750731549019</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.001937496119890378</v>
+        <v>0.001937496119890377</v>
       </c>
       <c r="BF8" t="n">
         <v>0.0006205459465706579</v>
@@ -3910,7 +3910,7 @@
         <v>0.007135654045493678</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.004877046792832895</v>
+        <v>0.004877046792832893</v>
       </c>
       <c r="BW8" t="n">
         <v>6.629607223229629e-05</v>
@@ -3919,7 +3919,7 @@
         <v>0.001389634701056285</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0001429060796106453</v>
+        <v>0.0001429060796106454</v>
       </c>
       <c r="BZ8" t="n">
         <v>0.0004515115020362483</v>
@@ -3937,7 +3937,7 @@
         <v>0.0006022402036714483</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.00472507487463618</v>
+        <v>0.004725074874636177</v>
       </c>
       <c r="CF8" t="n">
         <v>0.001497027922916348</v>
@@ -3971,7 +3971,7 @@
         <v>0.000302780589950839</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.003145549962840054</v>
+        <v>0.003145549962840058</v>
       </c>
       <c r="CR8" t="n">
         <v>0.001481937066036575</v>
@@ -3983,7 +3983,7 @@
         <v>0.0008746195265736432</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0008618986871498772</v>
+        <v>0.0008618986871498774</v>
       </c>
       <c r="CV8" t="n">
         <v>0.0005460731091987235</v>
@@ -3992,13 +3992,13 @@
         <v>0.0003511481905087565</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.005722606737096629</v>
+        <v>0.005722606737096633</v>
       </c>
       <c r="CY8" t="n">
         <v>0.0001162847030956305</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0003659159071259925</v>
+        <v>0.0003659159071259922</v>
       </c>
       <c r="DA8" t="n">
         <v>0.0009081493258358465</v>
@@ -4031,7 +4031,7 @@
         <v>0.0002478703805160941</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.002326331345566861</v>
+        <v>0.002326331345566862</v>
       </c>
       <c r="DL8" t="n">
         <v>0.0003418445490377975</v>
@@ -4046,7 +4046,7 @@
         <v>0.002277712373257225</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.12146303340133</v>
+        <v>0.1214630334013299</v>
       </c>
       <c r="DQ8" t="n">
         <v>3.487583679103902e-05</v>
@@ -4134,10 +4134,10 @@
         <v>0.03750738047849197</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1907120981083608</v>
+        <v>0.1907120981083607</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5496685814303734</v>
+        <v>0.5496685814303726</v>
       </c>
       <c r="H9" t="n">
         <v>0.2207414109251293</v>
@@ -4152,7 +4152,7 @@
         <v>0.03079461288405615</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02117371274387799</v>
+        <v>0.02117371274387798</v>
       </c>
       <c r="M9" t="n">
         <v>0.0012105427579708</v>
@@ -4167,7 +4167,7 @@
         <v>0.005126259861526819</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001401141914034413</v>
+        <v>0.001401141914034414</v>
       </c>
       <c r="R9" t="n">
         <v>0.00520478376564144</v>
@@ -4182,10 +4182,10 @@
         <v>0.0004139456050154632</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001597211759193014</v>
+        <v>0.001597211759193013</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02256622037028606</v>
+        <v>0.02256622037028605</v>
       </c>
       <c r="X9" t="n">
         <v>6.670812828262486e-05</v>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>0.07331464111748835</v>
+        <v>0.07331464111748832</v>
       </c>
       <c r="AG9" t="n">
         <v>0.01712898537081789</v>
@@ -4243,7 +4243,7 @@
         <v>0.0004933744634648337</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.002863984251159531</v>
+        <v>0.002863984251159532</v>
       </c>
       <c r="AR9" t="n">
         <v>0.002909682476050968</v>
@@ -4270,13 +4270,13 @@
         <v>0.05325073449241447</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.001215971012224929</v>
+        <v>0.00121597101222493</v>
       </c>
       <c r="BA9" t="n">
         <v>0.0001032013292345435</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.02313607226291884</v>
+        <v>0.02313607226291885</v>
       </c>
       <c r="BC9" t="n">
         <v>0.01028887474692199</v>
@@ -4291,7 +4291,7 @@
         <v>0.0005711725853708409</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.001507800072299827</v>
+        <v>0.001507800072299828</v>
       </c>
       <c r="BH9" t="n">
         <v>0.01050063902796607</v>
@@ -4303,13 +4303,13 @@
         <v>8.455439696789832e-06</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.005905954127979918</v>
+        <v>0.005905954127979915</v>
       </c>
       <c r="BL9" t="n">
         <v>0.0002619441498969066</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.05484892401085858</v>
+        <v>0.05484892401085861</v>
       </c>
       <c r="BN9" t="n">
         <v>0.001431115511164879</v>
@@ -4318,7 +4318,7 @@
         <v>8.738473092731573e-05</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0005508307610435388</v>
+        <v>0.000550830761043539</v>
       </c>
       <c r="BQ9" t="n">
         <v>0.0009905465247507525</v>
@@ -4339,7 +4339,7 @@
         <v>0.004789441832496292</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.649459748012629e-05</v>
+        <v>5.649459748012626e-05</v>
       </c>
       <c r="BX9" t="n">
         <v>0.001325638280169958</v>
@@ -4386,7 +4386,7 @@
         <v>3.075921413201157e-06</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0002307202165210258</v>
+        <v>0.0002307202165210257</v>
       </c>
       <c r="CO9" t="n">
         <v>0.003221518708789855</v>
@@ -4404,7 +4404,7 @@
         <v>0.0003293623245227471</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.0008570314316971442</v>
+        <v>0.000857031431697144</v>
       </c>
       <c r="CU9" t="n">
         <v>0.0007598064016171725</v>
@@ -4443,7 +4443,7 @@
         <v>0.0004297090654617939</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.006684728432040944</v>
+        <v>0.006684728432040946</v>
       </c>
       <c r="DH9" t="n">
         <v>0.001988555787870416</v>
@@ -4452,10 +4452,10 @@
         <v>0.0002365837805905561</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0002733633361407661</v>
+        <v>0.0002733633361407662</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.002397499887168333</v>
+        <v>0.002397499887168334</v>
       </c>
       <c r="DL9" t="n">
         <v>0.0003335178460416412</v>
@@ -4470,7 +4470,7 @@
         <v>0.001837933634751034</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.1369363309152135</v>
+        <v>0.1369363309152134</v>
       </c>
       <c r="DQ9" t="n">
         <v>3.0610853436831e-05</v>
@@ -4497,7 +4497,7 @@
         <v>0.0002310973132019088</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.0004802043524926367</v>
+        <v>0.000480204352492637</v>
       </c>
       <c r="DZ9" t="n">
         <v>0.0007523112365859861</v>
@@ -4558,10 +4558,10 @@
         <v>0.03801120453240394</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1938642856566679</v>
+        <v>0.193864285656668</v>
       </c>
       <c r="G10" t="n">
-        <v>0.561646553840488</v>
+        <v>0.5616465538404876</v>
       </c>
       <c r="H10" t="n">
         <v>0.2192887908827605</v>
@@ -4582,19 +4582,19 @@
         <v>0.001229281295114922</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01516941035734479</v>
+        <v>0.0151694103573448</v>
       </c>
       <c r="O10" t="n">
-        <v>0.00671926679238003</v>
+        <v>0.006719266792380027</v>
       </c>
       <c r="P10" t="n">
         <v>0.005188125519755827</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001415795468282523</v>
+        <v>0.001415795468282524</v>
       </c>
       <c r="R10" t="n">
-        <v>0.00510158002355141</v>
+        <v>0.005101580023551413</v>
       </c>
       <c r="S10" t="n">
         <v>0.005875524997887711</v>
@@ -4621,7 +4621,7 @@
         <v>0.001840863547634315</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0336408487969829</v>
+        <v>0.03364084879698288</v>
       </c>
       <c r="AB10" t="n">
         <v>0.0005749775010989074</v>
@@ -4637,7 +4637,7 @@
         <v>0.07547948916271659</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.01629070637299091</v>
+        <v>0.0162907063729909</v>
       </c>
       <c r="AH10" t="n">
         <v>0.002942721776315416</v>
@@ -4652,10 +4652,10 @@
         <v>0.02933269805027673</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.0009856941924634981</v>
+        <v>0.0009856941924634983</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0004757081192064583</v>
+        <v>0.0004757081192064585</v>
       </c>
       <c r="AN10" t="n">
         <v>0.0005035838858414486</v>
@@ -4667,7 +4667,7 @@
         <v>0.0004903257224071802</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.002936646216937171</v>
+        <v>0.00293664621693717</v>
       </c>
       <c r="AR10" t="n">
         <v>0.002885372934704096</v>
@@ -4691,7 +4691,7 @@
         <v>0.001615381895915035</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.05676411313976866</v>
+        <v>0.05676411313976862</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.001064194211362381</v>
@@ -4700,13 +4700,13 @@
         <v>0.0001175021847410314</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.02496882645357304</v>
+        <v>0.02496882645357303</v>
       </c>
       <c r="BC10" t="n">
         <v>0.01008102834929455</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.01403287809300752</v>
+        <v>0.01403287809300753</v>
       </c>
       <c r="BE10" t="n">
         <v>0.001768542813969982</v>
@@ -4715,7 +4715,7 @@
         <v>0.000532444071318263</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.001442547035906002</v>
+        <v>0.001442547035906001</v>
       </c>
       <c r="BH10" t="n">
         <v>0.01110055500312873</v>
@@ -4742,7 +4742,7 @@
         <v>8.125166704748208e-05</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0006553141696797698</v>
+        <v>0.0006553141696797702</v>
       </c>
       <c r="BQ10" t="n">
         <v>0.0009979119480334926</v>
@@ -4834,7 +4834,7 @@
         <v>0.0006338179170537162</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0004936894854624343</v>
+        <v>0.0004936894854624339</v>
       </c>
       <c r="CW10" t="n">
         <v>0.0003348697115424609</v>
@@ -4846,10 +4846,10 @@
         <v>0.0001073327981463217</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0003291934645548314</v>
+        <v>0.0003291934645548313</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.0008835153570420545</v>
+        <v>0.0008835153570420549</v>
       </c>
       <c r="DB10" t="n">
         <v>0.0003551876009555712</v>
@@ -4867,7 +4867,7 @@
         <v>0.0004771164007850931</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.006822130072525585</v>
+        <v>0.006822130072525582</v>
       </c>
       <c r="DH10" t="n">
         <v>0.001911106812128134</v>
@@ -4876,7 +4876,7 @@
         <v>0.0002368919348413701</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0002611078148595919</v>
+        <v>0.0002611078148595918</v>
       </c>
       <c r="DK10" t="n">
         <v>0.002405388230265301</v>
@@ -4903,7 +4903,7 @@
         <v>1.114062898117956e-05</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.00288299539197966</v>
+        <v>0.002882995391979661</v>
       </c>
       <c r="DT10" t="n">
         <v>0.001123254110532948</v>
